--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127043023</v>
+        <v>127045418</v>
       </c>
       <c r="B2" t="n">
-        <v>78739</v>
+        <v>78417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436949</v>
+        <v>436671</v>
       </c>
       <c r="R2" t="n">
-        <v>6852713</v>
+        <v>6852588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127045418</v>
+        <v>127043023</v>
       </c>
       <c r="B3" t="n">
-        <v>78386</v>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436671</v>
+        <v>436949</v>
       </c>
       <c r="R3" t="n">
-        <v>6852588</v>
+        <v>6852713</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127042916</v>
+        <v>127045435</v>
       </c>
       <c r="B4" t="n">
-        <v>79569</v>
+        <v>77989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436818</v>
+        <v>436671</v>
       </c>
       <c r="R4" t="n">
-        <v>6852702</v>
+        <v>6852588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127045435</v>
+        <v>127042916</v>
       </c>
       <c r="B5" t="n">
-        <v>77929</v>
+        <v>79600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436671</v>
+        <v>436818</v>
       </c>
       <c r="R5" t="n">
-        <v>6852588</v>
+        <v>6852702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>127045757</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127042774</v>
       </c>
       <c r="B8" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>127045829</v>
       </c>
       <c r="B9" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>127043219</v>
       </c>
       <c r="B10" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127042878</v>
       </c>
       <c r="B11" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>127042921</v>
       </c>
       <c r="B12" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>127045862</v>
       </c>
       <c r="B13" t="n">
-        <v>77929</v>
+        <v>77989</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>127044642</v>
       </c>
       <c r="B14" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>127042640</v>
       </c>
       <c r="B15" t="n">
-        <v>77929</v>
+        <v>77989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>127042961</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127042782</v>
+        <v>127043500</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436839</v>
+        <v>436900</v>
       </c>
       <c r="R17" t="n">
-        <v>6852857</v>
+        <v>6852768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2210,11 +2210,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2241,32 +2236,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127043500</v>
+        <v>127042782</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2276,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436900</v>
+        <v>436839</v>
       </c>
       <c r="R18" t="n">
-        <v>6852768</v>
+        <v>6852857</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2312,6 +2307,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2341,7 +2341,7 @@
         <v>127044529</v>
       </c>
       <c r="B19" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127043155</v>
+        <v>127044713</v>
       </c>
       <c r="B20" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437036</v>
+        <v>436697</v>
       </c>
       <c r="R20" t="n">
-        <v>6852766</v>
+        <v>6852687</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2535,7 +2535,7 @@
         <v>127042718</v>
       </c>
       <c r="B21" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127044760</v>
+        <v>127043155</v>
       </c>
       <c r="B22" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436777</v>
+        <v>437036</v>
       </c>
       <c r="R22" t="n">
-        <v>6852598</v>
+        <v>6852766</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127044713</v>
+        <v>127044760</v>
       </c>
       <c r="B23" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436697</v>
+        <v>436777</v>
       </c>
       <c r="R23" t="n">
-        <v>6852687</v>
+        <v>6852598</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127044451</v>
+        <v>127044491</v>
       </c>
       <c r="B24" t="n">
-        <v>78739</v>
+        <v>78769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436598</v>
+        <v>436623</v>
       </c>
       <c r="R24" t="n">
-        <v>6852836</v>
+        <v>6852823</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127044491</v>
+        <v>127043168</v>
       </c>
       <c r="B25" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436623</v>
+        <v>437048</v>
       </c>
       <c r="R25" t="n">
-        <v>6852823</v>
+        <v>6852775</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127043256</v>
+        <v>127044451</v>
       </c>
       <c r="B26" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437153</v>
+        <v>436598</v>
       </c>
       <c r="R26" t="n">
-        <v>6852858</v>
+        <v>6852836</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127043168</v>
+        <v>127042707</v>
       </c>
       <c r="B27" t="n">
-        <v>78738</v>
+        <v>78770</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437048</v>
+        <v>436693</v>
       </c>
       <c r="R27" t="n">
-        <v>6852775</v>
+        <v>6852823</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127042707</v>
+        <v>127043256</v>
       </c>
       <c r="B28" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436693</v>
+        <v>437153</v>
       </c>
       <c r="R28" t="n">
-        <v>6852823</v>
+        <v>6852858</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127043071</v>
+        <v>127043085</v>
       </c>
       <c r="B29" t="n">
-        <v>79569</v>
+        <v>56849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436968</v>
+        <v>436966</v>
       </c>
       <c r="R29" t="n">
-        <v>6852714</v>
+        <v>6852719</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3379,6 +3379,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3405,32 +3410,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127043085</v>
+        <v>127043071</v>
       </c>
       <c r="B30" t="n">
-        <v>56849</v>
+        <v>79600</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3445,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436966</v>
+        <v>436968</v>
       </c>
       <c r="R30" t="n">
-        <v>6852719</v>
+        <v>6852714</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3476,11 +3481,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127043130</v>
+        <v>127043039</v>
       </c>
       <c r="B31" t="n">
-        <v>78647</v>
+        <v>79600</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3518,21 +3518,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437025</v>
+        <v>436949</v>
       </c>
       <c r="R31" t="n">
-        <v>6852728</v>
+        <v>6852713</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127043039</v>
+        <v>127042769</v>
       </c>
       <c r="B32" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,13 +3639,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436949</v>
+        <v>436811</v>
       </c>
       <c r="R32" t="n">
-        <v>6852713</v>
+        <v>6852876</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127042769</v>
+        <v>127043130</v>
       </c>
       <c r="B33" t="n">
-        <v>79569</v>
+        <v>78678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3712,21 +3712,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3736,13 +3736,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436811</v>
+        <v>437025</v>
       </c>
       <c r="R33" t="n">
-        <v>6852876</v>
+        <v>6852728</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>127045928</v>
       </c>
       <c r="B34" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>127042693</v>
       </c>
       <c r="B36" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127045418</v>
       </c>
       <c r="B2" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127043023</v>
       </c>
       <c r="B3" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127045435</v>
       </c>
       <c r="B4" t="n">
-        <v>77989</v>
+        <v>77992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127042916</v>
       </c>
       <c r="B5" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127045757</v>
       </c>
       <c r="B6" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127042774</v>
+        <v>127045829</v>
       </c>
       <c r="B8" t="n">
-        <v>78770</v>
+        <v>79603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436811</v>
+        <v>436614</v>
       </c>
       <c r="R8" t="n">
-        <v>6852876</v>
+        <v>6852662</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127045829</v>
+        <v>127042774</v>
       </c>
       <c r="B9" t="n">
-        <v>79600</v>
+        <v>78773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436614</v>
+        <v>436811</v>
       </c>
       <c r="R9" t="n">
-        <v>6852662</v>
+        <v>6852876</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>127043219</v>
       </c>
       <c r="B10" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127042878</v>
+        <v>127045862</v>
       </c>
       <c r="B11" t="n">
-        <v>78770</v>
+        <v>77992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436744</v>
+        <v>436614</v>
       </c>
       <c r="R11" t="n">
-        <v>6852740</v>
+        <v>6852662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
         <v>127042921</v>
       </c>
       <c r="B12" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127045862</v>
+        <v>127042878</v>
       </c>
       <c r="B13" t="n">
-        <v>77989</v>
+        <v>78773</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436614</v>
+        <v>436744</v>
       </c>
       <c r="R13" t="n">
-        <v>6852662</v>
+        <v>6852740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,7 +1851,7 @@
         <v>127044642</v>
       </c>
       <c r="B14" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>127042640</v>
       </c>
       <c r="B15" t="n">
-        <v>77989</v>
+        <v>77992</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>127042961</v>
       </c>
       <c r="B16" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>127043500</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>127044529</v>
       </c>
       <c r="B19" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127044713</v>
+        <v>127043155</v>
       </c>
       <c r="B20" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436697</v>
+        <v>437036</v>
       </c>
       <c r="R20" t="n">
-        <v>6852687</v>
+        <v>6852766</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127042718</v>
+        <v>127044760</v>
       </c>
       <c r="B21" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436698</v>
+        <v>436777</v>
       </c>
       <c r="R21" t="n">
-        <v>6852807</v>
+        <v>6852598</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127043155</v>
+        <v>127044713</v>
       </c>
       <c r="B22" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437036</v>
+        <v>436697</v>
       </c>
       <c r="R22" t="n">
-        <v>6852766</v>
+        <v>6852687</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127044760</v>
+        <v>127042718</v>
       </c>
       <c r="B23" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436777</v>
+        <v>436698</v>
       </c>
       <c r="R23" t="n">
-        <v>6852598</v>
+        <v>6852807</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127044491</v>
+        <v>127043168</v>
       </c>
       <c r="B24" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436623</v>
+        <v>437048</v>
       </c>
       <c r="R24" t="n">
-        <v>6852823</v>
+        <v>6852775</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127043168</v>
+        <v>127044491</v>
       </c>
       <c r="B25" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437048</v>
+        <v>436623</v>
       </c>
       <c r="R25" t="n">
-        <v>6852775</v>
+        <v>6852823</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127044451</v>
+        <v>127042707</v>
       </c>
       <c r="B26" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436598</v>
+        <v>436693</v>
       </c>
       <c r="R26" t="n">
-        <v>6852836</v>
+        <v>6852823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127042707</v>
+        <v>127044451</v>
       </c>
       <c r="B27" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436693</v>
+        <v>436598</v>
       </c>
       <c r="R27" t="n">
-        <v>6852823</v>
+        <v>6852836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,7 +3214,7 @@
         <v>127043256</v>
       </c>
       <c r="B28" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127043085</v>
+        <v>127043071</v>
       </c>
       <c r="B29" t="n">
-        <v>56849</v>
+        <v>79603</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436966</v>
+        <v>436968</v>
       </c>
       <c r="R29" t="n">
-        <v>6852719</v>
+        <v>6852714</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3379,11 +3379,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3410,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127043071</v>
+        <v>127043085</v>
       </c>
       <c r="B30" t="n">
-        <v>79600</v>
+        <v>56849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3445,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436968</v>
+        <v>436966</v>
       </c>
       <c r="R30" t="n">
-        <v>6852714</v>
+        <v>6852719</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3481,6 +3476,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127043039</v>
+        <v>127043130</v>
       </c>
       <c r="B31" t="n">
-        <v>79600</v>
+        <v>78681</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3518,21 +3518,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436949</v>
+        <v>437025</v>
       </c>
       <c r="R31" t="n">
-        <v>6852713</v>
+        <v>6852728</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127042769</v>
+        <v>127043039</v>
       </c>
       <c r="B32" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,13 +3639,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436811</v>
+        <v>436949</v>
       </c>
       <c r="R32" t="n">
-        <v>6852876</v>
+        <v>6852713</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127043130</v>
+        <v>127042769</v>
       </c>
       <c r="B33" t="n">
-        <v>78678</v>
+        <v>79603</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3712,21 +3712,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3736,13 +3736,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437025</v>
+        <v>436811</v>
       </c>
       <c r="R33" t="n">
-        <v>6852728</v>
+        <v>6852876</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>127045928</v>
       </c>
       <c r="B34" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>127042693</v>
       </c>
       <c r="B36" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127045418</v>
+        <v>127043023</v>
       </c>
       <c r="B2" t="n">
-        <v>78420</v>
+        <v>78773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436671</v>
+        <v>436949</v>
       </c>
       <c r="R2" t="n">
-        <v>6852588</v>
+        <v>6852713</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127043023</v>
+        <v>127045418</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436949</v>
+        <v>436671</v>
       </c>
       <c r="R3" t="n">
-        <v>6852713</v>
+        <v>6852588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1160,54 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127043665</v>
+        <v>127045829</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>79603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436739</v>
+        <v>436614</v>
       </c>
       <c r="R7" t="n">
-        <v>6852982</v>
+        <v>6852662</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127045829</v>
+        <v>127042774</v>
       </c>
       <c r="B8" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436614</v>
+        <v>436811</v>
       </c>
       <c r="R8" t="n">
-        <v>6852662</v>
+        <v>6852876</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,48 +1354,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127042774</v>
+        <v>127043665</v>
       </c>
       <c r="B9" t="n">
-        <v>78773</v>
+        <v>57761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436811</v>
+        <v>436739</v>
       </c>
       <c r="R9" t="n">
-        <v>6852876</v>
+        <v>6852982</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127043168</v>
+        <v>127044491</v>
       </c>
       <c r="B24" t="n">
         <v>78772</v>
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437048</v>
+        <v>436623</v>
       </c>
       <c r="R24" t="n">
-        <v>6852775</v>
+        <v>6852823</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127044491</v>
+        <v>127043168</v>
       </c>
       <c r="B25" t="n">
         <v>78772</v>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436623</v>
+        <v>437048</v>
       </c>
       <c r="R25" t="n">
-        <v>6852823</v>
+        <v>6852775</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127043071</v>
+        <v>127043085</v>
       </c>
       <c r="B29" t="n">
-        <v>79603</v>
+        <v>56849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436968</v>
+        <v>436966</v>
       </c>
       <c r="R29" t="n">
-        <v>6852714</v>
+        <v>6852719</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3379,6 +3379,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3405,32 +3410,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127043085</v>
+        <v>127043071</v>
       </c>
       <c r="B30" t="n">
-        <v>56849</v>
+        <v>79603</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3445,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436966</v>
+        <v>436968</v>
       </c>
       <c r="R30" t="n">
-        <v>6852719</v>
+        <v>6852714</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3476,11 +3481,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127043130</v>
+        <v>127043039</v>
       </c>
       <c r="B31" t="n">
-        <v>78681</v>
+        <v>79603</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3518,21 +3518,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437025</v>
+        <v>436949</v>
       </c>
       <c r="R31" t="n">
-        <v>6852728</v>
+        <v>6852713</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3604,7 +3604,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127043039</v>
+        <v>127042769</v>
       </c>
       <c r="B32" t="n">
         <v>79603</v>
@@ -3639,13 +3639,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436949</v>
+        <v>436811</v>
       </c>
       <c r="R32" t="n">
-        <v>6852713</v>
+        <v>6852876</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127042769</v>
+        <v>127043130</v>
       </c>
       <c r="B33" t="n">
-        <v>79603</v>
+        <v>78681</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3712,21 +3712,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3736,13 +3736,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436811</v>
+        <v>437025</v>
       </c>
       <c r="R33" t="n">
-        <v>6852876</v>
+        <v>6852728</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127043023</v>
+        <v>127045418</v>
       </c>
       <c r="B2" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436949</v>
+        <v>436671</v>
       </c>
       <c r="R2" t="n">
-        <v>6852713</v>
+        <v>6852588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127045418</v>
+        <v>127043023</v>
       </c>
       <c r="B3" t="n">
-        <v>78420</v>
+        <v>78773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436671</v>
+        <v>436949</v>
       </c>
       <c r="R3" t="n">
-        <v>6852588</v>
+        <v>6852713</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1160,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127045829</v>
+        <v>127043665</v>
       </c>
       <c r="B7" t="n">
-        <v>79603</v>
+        <v>57761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436614</v>
+        <v>436739</v>
       </c>
       <c r="R7" t="n">
-        <v>6852662</v>
+        <v>6852982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,54 +1363,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127043665</v>
+        <v>127045829</v>
       </c>
       <c r="B9" t="n">
-        <v>57761</v>
+        <v>79603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436739</v>
+        <v>436614</v>
       </c>
       <c r="R9" t="n">
-        <v>6852982</v>
+        <v>6852662</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -3507,10 +3507,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127043039</v>
+        <v>127043130</v>
       </c>
       <c r="B31" t="n">
-        <v>79603</v>
+        <v>78681</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3518,21 +3518,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436949</v>
+        <v>437025</v>
       </c>
       <c r="R31" t="n">
-        <v>6852713</v>
+        <v>6852728</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3604,7 +3604,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127042769</v>
+        <v>127043039</v>
       </c>
       <c r="B32" t="n">
         <v>79603</v>
@@ -3639,13 +3639,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436811</v>
+        <v>436949</v>
       </c>
       <c r="R32" t="n">
-        <v>6852876</v>
+        <v>6852713</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127043130</v>
+        <v>127042769</v>
       </c>
       <c r="B33" t="n">
-        <v>78681</v>
+        <v>79603</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3712,21 +3712,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3736,13 +3736,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437025</v>
+        <v>436811</v>
       </c>
       <c r="R33" t="n">
-        <v>6852728</v>
+        <v>6852876</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1160,54 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127043665</v>
+        <v>127045829</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>79603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436739</v>
+        <v>436614</v>
       </c>
       <c r="R7" t="n">
-        <v>6852982</v>
+        <v>6852662</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,45 +1354,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127045829</v>
+        <v>127043665</v>
       </c>
       <c r="B9" t="n">
-        <v>79603</v>
+        <v>57761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436614</v>
+        <v>436739</v>
       </c>
       <c r="R9" t="n">
-        <v>6852662</v>
+        <v>6852982</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127045862</v>
+        <v>127042921</v>
       </c>
       <c r="B11" t="n">
-        <v>77992</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436614</v>
+        <v>436818</v>
       </c>
       <c r="R11" t="n">
-        <v>6852662</v>
+        <v>6852702</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127042921</v>
+        <v>127042878</v>
       </c>
       <c r="B12" t="n">
         <v>78773</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436818</v>
+        <v>436744</v>
       </c>
       <c r="R12" t="n">
-        <v>6852702</v>
+        <v>6852740</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127042878</v>
+        <v>127045862</v>
       </c>
       <c r="B13" t="n">
-        <v>78773</v>
+        <v>77992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436744</v>
+        <v>436614</v>
       </c>
       <c r="R13" t="n">
-        <v>6852740</v>
+        <v>6852662</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127044491</v>
+        <v>127042707</v>
       </c>
       <c r="B24" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436623</v>
+        <v>436693</v>
       </c>
       <c r="R24" t="n">
         <v>6852823</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127043168</v>
+        <v>127044451</v>
       </c>
       <c r="B25" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437048</v>
+        <v>436598</v>
       </c>
       <c r="R25" t="n">
-        <v>6852775</v>
+        <v>6852836</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127042707</v>
+        <v>127043256</v>
       </c>
       <c r="B26" t="n">
         <v>78773</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436693</v>
+        <v>437153</v>
       </c>
       <c r="R26" t="n">
-        <v>6852823</v>
+        <v>6852858</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127044451</v>
+        <v>127044491</v>
       </c>
       <c r="B27" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436598</v>
+        <v>436623</v>
       </c>
       <c r="R27" t="n">
-        <v>6852836</v>
+        <v>6852823</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127043256</v>
+        <v>127043168</v>
       </c>
       <c r="B28" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,13 +3246,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437153</v>
+        <v>437048</v>
       </c>
       <c r="R28" t="n">
-        <v>6852858</v>
+        <v>6852775</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1160,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127045829</v>
+        <v>127043665</v>
       </c>
       <c r="B7" t="n">
-        <v>79603</v>
+        <v>57761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436614</v>
+        <v>436739</v>
       </c>
       <c r="R7" t="n">
-        <v>6852662</v>
+        <v>6852982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127042774</v>
+        <v>127045829</v>
       </c>
       <c r="B8" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1301,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436811</v>
+        <v>436614</v>
       </c>
       <c r="R8" t="n">
-        <v>6852876</v>
+        <v>6852662</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1354,57 +1363,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127043665</v>
+        <v>127042774</v>
       </c>
       <c r="B9" t="n">
-        <v>57761</v>
+        <v>78773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436739</v>
+        <v>436811</v>
       </c>
       <c r="R9" t="n">
-        <v>6852982</v>
+        <v>6852876</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127042707</v>
+        <v>127044491</v>
       </c>
       <c r="B24" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436693</v>
+        <v>436623</v>
       </c>
       <c r="R24" t="n">
         <v>6852823</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127044451</v>
+        <v>127043168</v>
       </c>
       <c r="B25" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436598</v>
+        <v>437048</v>
       </c>
       <c r="R25" t="n">
-        <v>6852836</v>
+        <v>6852775</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127043256</v>
+        <v>127042707</v>
       </c>
       <c r="B26" t="n">
         <v>78773</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437153</v>
+        <v>436693</v>
       </c>
       <c r="R26" t="n">
-        <v>6852858</v>
+        <v>6852823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127044491</v>
+        <v>127044451</v>
       </c>
       <c r="B27" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436623</v>
+        <v>436598</v>
       </c>
       <c r="R27" t="n">
-        <v>6852823</v>
+        <v>6852836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127043168</v>
+        <v>127043256</v>
       </c>
       <c r="B28" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,13 +3246,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437048</v>
+        <v>437153</v>
       </c>
       <c r="R28" t="n">
-        <v>6852775</v>
+        <v>6852858</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127043085</v>
+        <v>127043071</v>
       </c>
       <c r="B29" t="n">
-        <v>56849</v>
+        <v>79603</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436966</v>
+        <v>436968</v>
       </c>
       <c r="R29" t="n">
-        <v>6852719</v>
+        <v>6852714</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3379,11 +3379,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3410,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127043071</v>
+        <v>127043085</v>
       </c>
       <c r="B30" t="n">
-        <v>79603</v>
+        <v>56849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3445,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436968</v>
+        <v>436966</v>
       </c>
       <c r="R30" t="n">
-        <v>6852714</v>
+        <v>6852719</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3481,6 +3476,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1160,54 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127043665</v>
+        <v>127045829</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>79603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436739</v>
+        <v>436614</v>
       </c>
       <c r="R7" t="n">
-        <v>6852982</v>
+        <v>6852662</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127045829</v>
+        <v>127042774</v>
       </c>
       <c r="B8" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436614</v>
+        <v>436811</v>
       </c>
       <c r="R8" t="n">
-        <v>6852662</v>
+        <v>6852876</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,48 +1354,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127042774</v>
+        <v>127043665</v>
       </c>
       <c r="B9" t="n">
-        <v>78773</v>
+        <v>57761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436811</v>
+        <v>436739</v>
       </c>
       <c r="R9" t="n">
-        <v>6852876</v>
+        <v>6852982</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127042921</v>
+        <v>127045862</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>77992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436818</v>
+        <v>436614</v>
       </c>
       <c r="R11" t="n">
-        <v>6852702</v>
+        <v>6852662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127045862</v>
+        <v>127042921</v>
       </c>
       <c r="B13" t="n">
-        <v>77992</v>
+        <v>78773</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436614</v>
+        <v>436818</v>
       </c>
       <c r="R13" t="n">
-        <v>6852662</v>
+        <v>6852702</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127042961</v>
+        <v>127043500</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436878</v>
+        <v>436900</v>
       </c>
       <c r="R16" t="n">
-        <v>6852688</v>
+        <v>6852768</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127043500</v>
+        <v>127042961</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436900</v>
+        <v>436878</v>
       </c>
       <c r="R17" t="n">
-        <v>6852768</v>
+        <v>6852688</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127044491</v>
+        <v>127043168</v>
       </c>
       <c r="B24" t="n">
         <v>78772</v>
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436623</v>
+        <v>437048</v>
       </c>
       <c r="R24" t="n">
-        <v>6852823</v>
+        <v>6852775</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127043168</v>
+        <v>127044491</v>
       </c>
       <c r="B25" t="n">
         <v>78772</v>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437048</v>
+        <v>436623</v>
       </c>
       <c r="R25" t="n">
-        <v>6852775</v>
+        <v>6852823</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127043071</v>
+        <v>127043085</v>
       </c>
       <c r="B29" t="n">
-        <v>79603</v>
+        <v>56849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436968</v>
+        <v>436966</v>
       </c>
       <c r="R29" t="n">
-        <v>6852714</v>
+        <v>6852719</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3379,6 +3379,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3405,32 +3410,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127043085</v>
+        <v>127043071</v>
       </c>
       <c r="B30" t="n">
-        <v>56849</v>
+        <v>79603</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3445,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436966</v>
+        <v>436968</v>
       </c>
       <c r="R30" t="n">
-        <v>6852719</v>
+        <v>6852714</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3476,11 +3481,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127045862</v>
+        <v>127042878</v>
       </c>
       <c r="B11" t="n">
-        <v>77992</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436614</v>
+        <v>436744</v>
       </c>
       <c r="R11" t="n">
-        <v>6852662</v>
+        <v>6852740</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127042878</v>
+        <v>127045862</v>
       </c>
       <c r="B12" t="n">
-        <v>78773</v>
+        <v>77992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436744</v>
+        <v>436614</v>
       </c>
       <c r="R12" t="n">
-        <v>6852740</v>
+        <v>6852662</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1160,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127045829</v>
+        <v>127043665</v>
       </c>
       <c r="B7" t="n">
-        <v>79603</v>
+        <v>57761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436614</v>
+        <v>436739</v>
       </c>
       <c r="R7" t="n">
-        <v>6852662</v>
+        <v>6852982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127042774</v>
+        <v>127045829</v>
       </c>
       <c r="B8" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1301,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436811</v>
+        <v>436614</v>
       </c>
       <c r="R8" t="n">
-        <v>6852876</v>
+        <v>6852662</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1354,57 +1363,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127043665</v>
+        <v>127042774</v>
       </c>
       <c r="B9" t="n">
-        <v>57761</v>
+        <v>78773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436739</v>
+        <v>436811</v>
       </c>
       <c r="R9" t="n">
-        <v>6852982</v>
+        <v>6852876</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127045418</v>
       </c>
       <c r="B2" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127043023</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127045435</v>
       </c>
       <c r="B4" t="n">
-        <v>77992</v>
+        <v>77996</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127042916</v>
       </c>
       <c r="B5" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127045757</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,54 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127043665</v>
+        <v>127045829</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>79607</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436739</v>
+        <v>436614</v>
       </c>
       <c r="R7" t="n">
-        <v>6852982</v>
+        <v>6852662</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127045829</v>
+        <v>127042774</v>
       </c>
       <c r="B8" t="n">
-        <v>79603</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436614</v>
+        <v>436811</v>
       </c>
       <c r="R8" t="n">
-        <v>6852662</v>
+        <v>6852876</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,48 +1354,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127042774</v>
+        <v>127043665</v>
       </c>
       <c r="B9" t="n">
-        <v>78773</v>
+        <v>57765</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436811</v>
+        <v>436739</v>
       </c>
       <c r="R9" t="n">
-        <v>6852876</v>
+        <v>6852982</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>127043219</v>
       </c>
       <c r="B10" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127042878</v>
+        <v>127045862</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>77996</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436744</v>
+        <v>436614</v>
       </c>
       <c r="R11" t="n">
-        <v>6852740</v>
+        <v>6852662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127045862</v>
+        <v>127042921</v>
       </c>
       <c r="B12" t="n">
-        <v>77992</v>
+        <v>78777</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436614</v>
+        <v>436818</v>
       </c>
       <c r="R12" t="n">
-        <v>6852662</v>
+        <v>6852702</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127042921</v>
+        <v>127042878</v>
       </c>
       <c r="B13" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436818</v>
+        <v>436744</v>
       </c>
       <c r="R13" t="n">
-        <v>6852702</v>
+        <v>6852740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,7 +1851,7 @@
         <v>127044642</v>
       </c>
       <c r="B14" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>127042640</v>
       </c>
       <c r="B15" t="n">
-        <v>77992</v>
+        <v>77996</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127043500</v>
+        <v>127042961</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436900</v>
+        <v>436878</v>
       </c>
       <c r="R16" t="n">
-        <v>6852768</v>
+        <v>6852688</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127042961</v>
+        <v>127043500</v>
       </c>
       <c r="B17" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436878</v>
+        <v>436900</v>
       </c>
       <c r="R17" t="n">
-        <v>6852688</v>
+        <v>6852768</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>127042782</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>127044529</v>
       </c>
       <c r="B19" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>127043155</v>
       </c>
       <c r="B20" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>127044760</v>
       </c>
       <c r="B21" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127044713</v>
       </c>
       <c r="B22" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>127042718</v>
       </c>
       <c r="B23" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127043168</v>
+        <v>127042707</v>
       </c>
       <c r="B24" t="n">
-        <v>78772</v>
+        <v>78777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437048</v>
+        <v>436693</v>
       </c>
       <c r="R24" t="n">
-        <v>6852775</v>
+        <v>6852823</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127044491</v>
+        <v>127044451</v>
       </c>
       <c r="B25" t="n">
-        <v>78772</v>
+        <v>78777</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436623</v>
+        <v>436598</v>
       </c>
       <c r="R25" t="n">
-        <v>6852823</v>
+        <v>6852836</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127042707</v>
+        <v>127043256</v>
       </c>
       <c r="B26" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436693</v>
+        <v>437153</v>
       </c>
       <c r="R26" t="n">
-        <v>6852823</v>
+        <v>6852858</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127044451</v>
+        <v>127043168</v>
       </c>
       <c r="B27" t="n">
-        <v>78773</v>
+        <v>78776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436598</v>
+        <v>437048</v>
       </c>
       <c r="R27" t="n">
-        <v>6852836</v>
+        <v>6852775</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127043256</v>
+        <v>127044491</v>
       </c>
       <c r="B28" t="n">
-        <v>78773</v>
+        <v>78776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437153</v>
+        <v>436623</v>
       </c>
       <c r="R28" t="n">
-        <v>6852858</v>
+        <v>6852823</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
         <v>127043085</v>
       </c>
       <c r="B29" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>127043071</v>
       </c>
       <c r="B30" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>127043130</v>
       </c>
       <c r="B31" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>127043039</v>
       </c>
       <c r="B32" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>127042769</v>
       </c>
       <c r="B33" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>127045928</v>
       </c>
       <c r="B34" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>127042671</v>
       </c>
       <c r="B35" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>127042693</v>
       </c>
       <c r="B36" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127045435</v>
+        <v>127042916</v>
       </c>
       <c r="B4" t="n">
-        <v>77996</v>
+        <v>79607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436671</v>
+        <v>436818</v>
       </c>
       <c r="R4" t="n">
-        <v>6852588</v>
+        <v>6852702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127042916</v>
+        <v>127045435</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>77996</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436818</v>
+        <v>436671</v>
       </c>
       <c r="R5" t="n">
-        <v>6852702</v>
+        <v>6852588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127045829</v>
+        <v>127043665</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>57765</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436614</v>
+        <v>436739</v>
       </c>
       <c r="R7" t="n">
-        <v>6852662</v>
+        <v>6852982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,54 +1363,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127043665</v>
+        <v>127045829</v>
       </c>
       <c r="B9" t="n">
-        <v>57765</v>
+        <v>79607</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436739</v>
+        <v>436614</v>
       </c>
       <c r="R9" t="n">
-        <v>6852982</v>
+        <v>6852662</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127042921</v>
+        <v>127042878</v>
       </c>
       <c r="B12" t="n">
         <v>78777</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436818</v>
+        <v>436744</v>
       </c>
       <c r="R12" t="n">
-        <v>6852702</v>
+        <v>6852740</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127042878</v>
+        <v>127042921</v>
       </c>
       <c r="B13" t="n">
         <v>78777</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436744</v>
+        <v>436818</v>
       </c>
       <c r="R13" t="n">
-        <v>6852740</v>
+        <v>6852702</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127042707</v>
+        <v>127043168</v>
       </c>
       <c r="B24" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436693</v>
+        <v>437048</v>
       </c>
       <c r="R24" t="n">
-        <v>6852823</v>
+        <v>6852775</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127044451</v>
+        <v>127044491</v>
       </c>
       <c r="B25" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436598</v>
+        <v>436623</v>
       </c>
       <c r="R25" t="n">
-        <v>6852836</v>
+        <v>6852823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127043256</v>
+        <v>127042707</v>
       </c>
       <c r="B26" t="n">
         <v>78777</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437153</v>
+        <v>436693</v>
       </c>
       <c r="R26" t="n">
-        <v>6852858</v>
+        <v>6852823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127043168</v>
+        <v>127044451</v>
       </c>
       <c r="B27" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437048</v>
+        <v>436598</v>
       </c>
       <c r="R27" t="n">
-        <v>6852775</v>
+        <v>6852836</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127044491</v>
+        <v>127043256</v>
       </c>
       <c r="B28" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436623</v>
+        <v>437153</v>
       </c>
       <c r="R28" t="n">
-        <v>6852823</v>
+        <v>6852858</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,10 +3507,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127043130</v>
+        <v>127043039</v>
       </c>
       <c r="B31" t="n">
-        <v>78685</v>
+        <v>79607</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3518,21 +3518,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437025</v>
+        <v>436949</v>
       </c>
       <c r="R31" t="n">
-        <v>6852728</v>
+        <v>6852713</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3604,7 +3604,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127043039</v>
+        <v>127042769</v>
       </c>
       <c r="B32" t="n">
         <v>79607</v>
@@ -3639,13 +3639,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436949</v>
+        <v>436811</v>
       </c>
       <c r="R32" t="n">
-        <v>6852713</v>
+        <v>6852876</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127042769</v>
+        <v>127043130</v>
       </c>
       <c r="B33" t="n">
-        <v>79607</v>
+        <v>78685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3712,21 +3712,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3736,13 +3736,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436811</v>
+        <v>437025</v>
       </c>
       <c r="R33" t="n">
-        <v>6852876</v>
+        <v>6852728</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127045862</v>
+        <v>127042921</v>
       </c>
       <c r="B11" t="n">
-        <v>77996</v>
+        <v>78777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436614</v>
+        <v>436818</v>
       </c>
       <c r="R11" t="n">
-        <v>6852662</v>
+        <v>6852702</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127042921</v>
+        <v>127045862</v>
       </c>
       <c r="B13" t="n">
-        <v>78777</v>
+        <v>77996</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436818</v>
+        <v>436614</v>
       </c>
       <c r="R13" t="n">
-        <v>6852702</v>
+        <v>6852662</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127043168</v>
+        <v>127043256</v>
       </c>
       <c r="B24" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437048</v>
+        <v>437153</v>
       </c>
       <c r="R24" t="n">
-        <v>6852775</v>
+        <v>6852858</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127044491</v>
+        <v>127042707</v>
       </c>
       <c r="B25" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436623</v>
+        <v>436693</v>
       </c>
       <c r="R25" t="n">
         <v>6852823</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127042707</v>
+        <v>127044451</v>
       </c>
       <c r="B26" t="n">
         <v>78777</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436693</v>
+        <v>436598</v>
       </c>
       <c r="R26" t="n">
-        <v>6852823</v>
+        <v>6852836</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127044451</v>
+        <v>127043168</v>
       </c>
       <c r="B27" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436598</v>
+        <v>437048</v>
       </c>
       <c r="R27" t="n">
-        <v>6852836</v>
+        <v>6852775</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127043256</v>
+        <v>127044491</v>
       </c>
       <c r="B28" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437153</v>
+        <v>436623</v>
       </c>
       <c r="R28" t="n">
-        <v>6852858</v>
+        <v>6852823</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127043085</v>
+        <v>127043071</v>
       </c>
       <c r="B29" t="n">
-        <v>56853</v>
+        <v>79607</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436966</v>
+        <v>436968</v>
       </c>
       <c r="R29" t="n">
-        <v>6852719</v>
+        <v>6852714</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3379,11 +3379,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3410,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127043071</v>
+        <v>127043085</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>56853</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3445,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436968</v>
+        <v>436966</v>
       </c>
       <c r="R30" t="n">
-        <v>6852714</v>
+        <v>6852719</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3481,6 +3476,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127043256</v>
+        <v>127043168</v>
       </c>
       <c r="B24" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437153</v>
+        <v>437048</v>
       </c>
       <c r="R24" t="n">
-        <v>6852858</v>
+        <v>6852775</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127042707</v>
+        <v>127044491</v>
       </c>
       <c r="B25" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436693</v>
+        <v>436623</v>
       </c>
       <c r="R25" t="n">
         <v>6852823</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127044451</v>
+        <v>127042707</v>
       </c>
       <c r="B26" t="n">
         <v>78777</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436598</v>
+        <v>436693</v>
       </c>
       <c r="R26" t="n">
-        <v>6852836</v>
+        <v>6852823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127043168</v>
+        <v>127044451</v>
       </c>
       <c r="B27" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437048</v>
+        <v>436598</v>
       </c>
       <c r="R27" t="n">
-        <v>6852775</v>
+        <v>6852836</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127044491</v>
+        <v>127043256</v>
       </c>
       <c r="B28" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436623</v>
+        <v>437153</v>
       </c>
       <c r="R28" t="n">
-        <v>6852823</v>
+        <v>6852858</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127043071</v>
+        <v>127043085</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>56853</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436968</v>
+        <v>436966</v>
       </c>
       <c r="R29" t="n">
-        <v>6852714</v>
+        <v>6852719</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3379,6 +3379,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3405,32 +3410,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127043085</v>
+        <v>127043071</v>
       </c>
       <c r="B30" t="n">
-        <v>56853</v>
+        <v>79607</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3445,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436966</v>
+        <v>436968</v>
       </c>
       <c r="R30" t="n">
-        <v>6852719</v>
+        <v>6852714</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3476,11 +3481,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127043039</v>
+        <v>127043130</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>78685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3518,21 +3518,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436949</v>
+        <v>437025</v>
       </c>
       <c r="R31" t="n">
-        <v>6852713</v>
+        <v>6852728</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3604,7 +3604,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127042769</v>
+        <v>127043039</v>
       </c>
       <c r="B32" t="n">
         <v>79607</v>
@@ -3639,13 +3639,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436811</v>
+        <v>436949</v>
       </c>
       <c r="R32" t="n">
-        <v>6852876</v>
+        <v>6852713</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127043130</v>
+        <v>127042769</v>
       </c>
       <c r="B33" t="n">
-        <v>78685</v>
+        <v>79607</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3712,21 +3712,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3736,13 +3736,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437025</v>
+        <v>436811</v>
       </c>
       <c r="R33" t="n">
-        <v>6852728</v>
+        <v>6852876</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127042916</v>
+        <v>127045435</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>77996</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436818</v>
+        <v>436671</v>
       </c>
       <c r="R4" t="n">
-        <v>6852702</v>
+        <v>6852588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127045435</v>
+        <v>127042916</v>
       </c>
       <c r="B5" t="n">
-        <v>77996</v>
+        <v>79607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436671</v>
+        <v>436818</v>
       </c>
       <c r="R5" t="n">
-        <v>6852588</v>
+        <v>6852702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,57 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127043665</v>
+        <v>127042774</v>
       </c>
       <c r="B7" t="n">
-        <v>57765</v>
+        <v>78777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436739</v>
+        <v>436811</v>
       </c>
       <c r="R7" t="n">
-        <v>6852982</v>
+        <v>6852876</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1266,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127042774</v>
+        <v>127045829</v>
       </c>
       <c r="B8" t="n">
-        <v>78777</v>
+        <v>79607</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436811</v>
+        <v>436614</v>
       </c>
       <c r="R8" t="n">
-        <v>6852876</v>
+        <v>6852662</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,45 +1354,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127045829</v>
+        <v>127043665</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>57765</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436614</v>
+        <v>436739</v>
       </c>
       <c r="R9" t="n">
-        <v>6852662</v>
+        <v>6852982</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127042921</v>
+        <v>127045862</v>
       </c>
       <c r="B11" t="n">
-        <v>78777</v>
+        <v>77996</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436818</v>
+        <v>436614</v>
       </c>
       <c r="R11" t="n">
-        <v>6852702</v>
+        <v>6852662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127045862</v>
+        <v>127042921</v>
       </c>
       <c r="B13" t="n">
-        <v>77996</v>
+        <v>78777</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436614</v>
+        <v>436818</v>
       </c>
       <c r="R13" t="n">
-        <v>6852662</v>
+        <v>6852702</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127043155</v>
+        <v>127044713</v>
       </c>
       <c r="B20" t="n">
         <v>78777</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437036</v>
+        <v>436697</v>
       </c>
       <c r="R20" t="n">
-        <v>6852766</v>
+        <v>6852687</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127044760</v>
+        <v>127043155</v>
       </c>
       <c r="B21" t="n">
         <v>78777</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436777</v>
+        <v>437036</v>
       </c>
       <c r="R21" t="n">
-        <v>6852598</v>
+        <v>6852766</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127044713</v>
+        <v>127044760</v>
       </c>
       <c r="B22" t="n">
         <v>78777</v>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436697</v>
+        <v>436777</v>
       </c>
       <c r="R22" t="n">
-        <v>6852687</v>
+        <v>6852598</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127042707</v>
+        <v>127043256</v>
       </c>
       <c r="B26" t="n">
         <v>78777</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436693</v>
+        <v>437153</v>
       </c>
       <c r="R26" t="n">
-        <v>6852823</v>
+        <v>6852858</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,7 +3114,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127044451</v>
+        <v>127042707</v>
       </c>
       <c r="B27" t="n">
         <v>78777</v>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436598</v>
+        <v>436693</v>
       </c>
       <c r="R27" t="n">
-        <v>6852836</v>
+        <v>6852823</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,7 +3211,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127043256</v>
+        <v>127044451</v>
       </c>
       <c r="B28" t="n">
         <v>78777</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437153</v>
+        <v>436598</v>
       </c>
       <c r="R28" t="n">
-        <v>6852858</v>
+        <v>6852836</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3895,52 +3895,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127042671</v>
+        <v>127042693</v>
       </c>
       <c r="B35" t="n">
-        <v>56853</v>
+        <v>78777</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436712</v>
+        <v>436690</v>
       </c>
       <c r="R35" t="n">
-        <v>6852917</v>
+        <v>6852851</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3996,48 +3992,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127042693</v>
+        <v>127042671</v>
       </c>
       <c r="B36" t="n">
-        <v>78777</v>
+        <v>56853</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436690</v>
+        <v>436712</v>
       </c>
       <c r="R36" t="n">
-        <v>6852851</v>
+        <v>6852917</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1257,45 +1257,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127045829</v>
+        <v>127043665</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>57765</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436614</v>
+        <v>436739</v>
       </c>
       <c r="R8" t="n">
-        <v>6852662</v>
+        <v>6852982</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,54 +1363,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127043665</v>
+        <v>127045829</v>
       </c>
       <c r="B9" t="n">
-        <v>57765</v>
+        <v>79607</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436739</v>
+        <v>436614</v>
       </c>
       <c r="R9" t="n">
-        <v>6852982</v>
+        <v>6852662</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127044713</v>
+        <v>127043155</v>
       </c>
       <c r="B20" t="n">
         <v>78777</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436697</v>
+        <v>437036</v>
       </c>
       <c r="R20" t="n">
-        <v>6852687</v>
+        <v>6852766</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127043155</v>
+        <v>127044760</v>
       </c>
       <c r="B21" t="n">
         <v>78777</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437036</v>
+        <v>436777</v>
       </c>
       <c r="R21" t="n">
-        <v>6852766</v>
+        <v>6852598</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127044760</v>
+        <v>127042718</v>
       </c>
       <c r="B22" t="n">
         <v>78777</v>
@@ -2664,13 +2664,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436777</v>
+        <v>436698</v>
       </c>
       <c r="R22" t="n">
-        <v>6852598</v>
+        <v>6852807</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127042718</v>
+        <v>127044713</v>
       </c>
       <c r="B23" t="n">
         <v>78777</v>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436698</v>
+        <v>436697</v>
       </c>
       <c r="R23" t="n">
-        <v>6852807</v>
+        <v>6852687</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127045418</v>
       </c>
       <c r="B2" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127043023</v>
       </c>
       <c r="B3" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127045435</v>
+        <v>127042916</v>
       </c>
       <c r="B4" t="n">
-        <v>77996</v>
+        <v>79609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436671</v>
+        <v>436818</v>
       </c>
       <c r="R4" t="n">
-        <v>6852588</v>
+        <v>6852702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127042916</v>
+        <v>127045435</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>77998</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436818</v>
+        <v>436671</v>
       </c>
       <c r="R5" t="n">
-        <v>6852702</v>
+        <v>6852588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>127045757</v>
       </c>
       <c r="B6" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,48 +1160,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127042774</v>
+        <v>127043665</v>
       </c>
       <c r="B7" t="n">
-        <v>78777</v>
+        <v>57767</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436811</v>
+        <v>436739</v>
       </c>
       <c r="R7" t="n">
-        <v>6852876</v>
+        <v>6852982</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,57 +1266,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127043665</v>
+        <v>127042774</v>
       </c>
       <c r="B8" t="n">
-        <v>57765</v>
+        <v>78779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436739</v>
+        <v>436811</v>
       </c>
       <c r="R8" t="n">
-        <v>6852982</v>
+        <v>6852876</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>127045829</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>127043219</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127045862</v>
       </c>
       <c r="B11" t="n">
-        <v>77996</v>
+        <v>77998</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127042878</v>
+        <v>127042921</v>
       </c>
       <c r="B12" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436744</v>
+        <v>436818</v>
       </c>
       <c r="R12" t="n">
-        <v>6852740</v>
+        <v>6852702</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127042921</v>
+        <v>127042878</v>
       </c>
       <c r="B13" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436818</v>
+        <v>436744</v>
       </c>
       <c r="R13" t="n">
-        <v>6852702</v>
+        <v>6852740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,7 +1851,7 @@
         <v>127044642</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>127042640</v>
       </c>
       <c r="B15" t="n">
-        <v>77996</v>
+        <v>77998</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>127042961</v>
       </c>
       <c r="B16" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>127043500</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>127042782</v>
       </c>
       <c r="B18" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>127044529</v>
       </c>
       <c r="B19" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>127043155</v>
       </c>
       <c r="B20" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>127044760</v>
       </c>
       <c r="B21" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127042718</v>
+        <v>127044713</v>
       </c>
       <c r="B22" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,13 +2664,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436698</v>
+        <v>436697</v>
       </c>
       <c r="R22" t="n">
-        <v>6852807</v>
+        <v>6852687</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127044713</v>
+        <v>127042718</v>
       </c>
       <c r="B23" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436697</v>
+        <v>436698</v>
       </c>
       <c r="R23" t="n">
-        <v>6852687</v>
+        <v>6852807</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127043168</v>
+        <v>127044491</v>
       </c>
       <c r="B24" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437048</v>
+        <v>436623</v>
       </c>
       <c r="R24" t="n">
-        <v>6852775</v>
+        <v>6852823</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127044491</v>
+        <v>127043168</v>
       </c>
       <c r="B25" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436623</v>
+        <v>437048</v>
       </c>
       <c r="R25" t="n">
-        <v>6852823</v>
+        <v>6852775</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127043256</v>
+        <v>127042707</v>
       </c>
       <c r="B26" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437153</v>
+        <v>436693</v>
       </c>
       <c r="R26" t="n">
-        <v>6852858</v>
+        <v>6852823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127042707</v>
+        <v>127044451</v>
       </c>
       <c r="B27" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436693</v>
+        <v>436598</v>
       </c>
       <c r="R27" t="n">
-        <v>6852823</v>
+        <v>6852836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127044451</v>
+        <v>127043256</v>
       </c>
       <c r="B28" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436598</v>
+        <v>437153</v>
       </c>
       <c r="R28" t="n">
-        <v>6852836</v>
+        <v>6852858</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127043085</v>
+        <v>127043071</v>
       </c>
       <c r="B29" t="n">
-        <v>56853</v>
+        <v>79609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436966</v>
+        <v>436968</v>
       </c>
       <c r="R29" t="n">
-        <v>6852719</v>
+        <v>6852714</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3379,11 +3379,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3410,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127043071</v>
+        <v>127043085</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>56855</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3445,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436968</v>
+        <v>436966</v>
       </c>
       <c r="R30" t="n">
-        <v>6852714</v>
+        <v>6852719</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3481,6 +3476,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127043130</v>
+        <v>127043039</v>
       </c>
       <c r="B31" t="n">
-        <v>78685</v>
+        <v>79609</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3518,21 +3518,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437025</v>
+        <v>436949</v>
       </c>
       <c r="R31" t="n">
-        <v>6852728</v>
+        <v>6852713</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127043039</v>
+        <v>127042769</v>
       </c>
       <c r="B32" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,13 +3639,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436949</v>
+        <v>436811</v>
       </c>
       <c r="R32" t="n">
-        <v>6852713</v>
+        <v>6852876</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127042769</v>
+        <v>127043130</v>
       </c>
       <c r="B33" t="n">
-        <v>79607</v>
+        <v>78687</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3712,21 +3712,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3736,13 +3736,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436811</v>
+        <v>437025</v>
       </c>
       <c r="R33" t="n">
-        <v>6852876</v>
+        <v>6852728</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>127045928</v>
       </c>
       <c r="B34" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3895,48 +3895,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127042693</v>
+        <v>127042671</v>
       </c>
       <c r="B35" t="n">
-        <v>78777</v>
+        <v>56855</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436690</v>
+        <v>436712</v>
       </c>
       <c r="R35" t="n">
-        <v>6852851</v>
+        <v>6852917</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3992,52 +3996,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127042671</v>
+        <v>127042693</v>
       </c>
       <c r="B36" t="n">
-        <v>56853</v>
+        <v>78779</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436712</v>
+        <v>436690</v>
       </c>
       <c r="R36" t="n">
-        <v>6852917</v>
+        <v>6852851</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127042916</v>
+        <v>127045435</v>
       </c>
       <c r="B4" t="n">
-        <v>79609</v>
+        <v>77998</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436818</v>
+        <v>436671</v>
       </c>
       <c r="R4" t="n">
-        <v>6852702</v>
+        <v>6852588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127045435</v>
+        <v>127042916</v>
       </c>
       <c r="B5" t="n">
-        <v>77998</v>
+        <v>79609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436671</v>
+        <v>436818</v>
       </c>
       <c r="R5" t="n">
-        <v>6852588</v>
+        <v>6852702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127042774</v>
+        <v>127045829</v>
       </c>
       <c r="B8" t="n">
-        <v>78779</v>
+        <v>79609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436811</v>
+        <v>436614</v>
       </c>
       <c r="R8" t="n">
-        <v>6852876</v>
+        <v>6852662</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127045829</v>
+        <v>127042774</v>
       </c>
       <c r="B9" t="n">
-        <v>79609</v>
+        <v>78779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436614</v>
+        <v>436811</v>
       </c>
       <c r="R9" t="n">
-        <v>6852662</v>
+        <v>6852876</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127042921</v>
+        <v>127042878</v>
       </c>
       <c r="B12" t="n">
         <v>78779</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436818</v>
+        <v>436744</v>
       </c>
       <c r="R12" t="n">
-        <v>6852702</v>
+        <v>6852740</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127042878</v>
+        <v>127042921</v>
       </c>
       <c r="B13" t="n">
         <v>78779</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436744</v>
+        <v>436818</v>
       </c>
       <c r="R13" t="n">
-        <v>6852740</v>
+        <v>6852702</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127042961</v>
+        <v>127042782</v>
       </c>
       <c r="B16" t="n">
-        <v>79638</v>
+        <v>56855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436878</v>
+        <v>436839</v>
       </c>
       <c r="R16" t="n">
-        <v>6852688</v>
+        <v>6852857</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2113,6 +2113,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2139,10 +2144,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127043500</v>
+        <v>127042961</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2155,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,13 +2179,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436900</v>
+        <v>436878</v>
       </c>
       <c r="R17" t="n">
-        <v>6852768</v>
+        <v>6852688</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2236,32 +2241,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127042782</v>
+        <v>127043500</v>
       </c>
       <c r="B18" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436839</v>
+        <v>436900</v>
       </c>
       <c r="R18" t="n">
-        <v>6852857</v>
+        <v>6852768</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2307,11 +2312,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127044491</v>
+        <v>127042707</v>
       </c>
       <c r="B24" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436623</v>
+        <v>436693</v>
       </c>
       <c r="R24" t="n">
         <v>6852823</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127043168</v>
+        <v>127044451</v>
       </c>
       <c r="B25" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437048</v>
+        <v>436598</v>
       </c>
       <c r="R25" t="n">
-        <v>6852775</v>
+        <v>6852836</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127042707</v>
+        <v>127043256</v>
       </c>
       <c r="B26" t="n">
         <v>78779</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436693</v>
+        <v>437153</v>
       </c>
       <c r="R26" t="n">
-        <v>6852823</v>
+        <v>6852858</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127044451</v>
+        <v>127043168</v>
       </c>
       <c r="B27" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436598</v>
+        <v>437048</v>
       </c>
       <c r="R27" t="n">
-        <v>6852836</v>
+        <v>6852775</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127043256</v>
+        <v>127044491</v>
       </c>
       <c r="B28" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437153</v>
+        <v>436623</v>
       </c>
       <c r="R28" t="n">
-        <v>6852858</v>
+        <v>6852823</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127043071</v>
+        <v>127043085</v>
       </c>
       <c r="B29" t="n">
-        <v>79609</v>
+        <v>56855</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436968</v>
+        <v>436966</v>
       </c>
       <c r="R29" t="n">
-        <v>6852714</v>
+        <v>6852719</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3379,6 +3379,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3405,32 +3410,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127043085</v>
+        <v>127043071</v>
       </c>
       <c r="B30" t="n">
-        <v>56855</v>
+        <v>79609</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3445,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436966</v>
+        <v>436968</v>
       </c>
       <c r="R30" t="n">
-        <v>6852719</v>
+        <v>6852714</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3476,11 +3481,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127043039</v>
+        <v>127043130</v>
       </c>
       <c r="B31" t="n">
-        <v>79609</v>
+        <v>78687</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3518,21 +3518,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436949</v>
+        <v>437025</v>
       </c>
       <c r="R31" t="n">
-        <v>6852713</v>
+        <v>6852728</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127043130</v>
+        <v>127043039</v>
       </c>
       <c r="B33" t="n">
-        <v>78687</v>
+        <v>79609</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3712,21 +3712,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3736,10 +3736,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437025</v>
+        <v>436949</v>
       </c>
       <c r="R33" t="n">
-        <v>6852728</v>
+        <v>6852713</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -1654,7 +1654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127042878</v>
+        <v>127042921</v>
       </c>
       <c r="B12" t="n">
         <v>78779</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436744</v>
+        <v>436818</v>
       </c>
       <c r="R12" t="n">
-        <v>6852740</v>
+        <v>6852702</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127042921</v>
+        <v>127042878</v>
       </c>
       <c r="B13" t="n">
         <v>78779</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436818</v>
+        <v>436744</v>
       </c>
       <c r="R13" t="n">
-        <v>6852702</v>
+        <v>6852740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127045435</v>
+        <v>127042916</v>
       </c>
       <c r="B4" t="n">
-        <v>77998</v>
+        <v>79609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436671</v>
+        <v>436818</v>
       </c>
       <c r="R4" t="n">
-        <v>6852588</v>
+        <v>6852702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127042916</v>
+        <v>127045435</v>
       </c>
       <c r="B5" t="n">
-        <v>79609</v>
+        <v>77998</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436818</v>
+        <v>436671</v>
       </c>
       <c r="R5" t="n">
-        <v>6852702</v>
+        <v>6852588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,54 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127043665</v>
+        <v>127045829</v>
       </c>
       <c r="B7" t="n">
-        <v>57767</v>
+        <v>79609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436739</v>
+        <v>436614</v>
       </c>
       <c r="R7" t="n">
-        <v>6852982</v>
+        <v>6852662</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127045829</v>
+        <v>127042774</v>
       </c>
       <c r="B8" t="n">
-        <v>79609</v>
+        <v>78779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436614</v>
+        <v>436811</v>
       </c>
       <c r="R8" t="n">
-        <v>6852662</v>
+        <v>6852876</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,48 +1354,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127042774</v>
+        <v>127043665</v>
       </c>
       <c r="B9" t="n">
-        <v>78779</v>
+        <v>57767</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436811</v>
+        <v>436739</v>
       </c>
       <c r="R9" t="n">
-        <v>6852876</v>
+        <v>6852982</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127045862</v>
+        <v>127042921</v>
       </c>
       <c r="B11" t="n">
-        <v>77998</v>
+        <v>78779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436614</v>
+        <v>436818</v>
       </c>
       <c r="R11" t="n">
-        <v>6852662</v>
+        <v>6852702</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127042921</v>
+        <v>127042878</v>
       </c>
       <c r="B12" t="n">
         <v>78779</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436818</v>
+        <v>436744</v>
       </c>
       <c r="R12" t="n">
-        <v>6852702</v>
+        <v>6852740</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127042878</v>
+        <v>127045862</v>
       </c>
       <c r="B13" t="n">
-        <v>78779</v>
+        <v>77998</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436744</v>
+        <v>436614</v>
       </c>
       <c r="R13" t="n">
-        <v>6852740</v>
+        <v>6852662</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127042707</v>
+        <v>127043168</v>
       </c>
       <c r="B24" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436693</v>
+        <v>437048</v>
       </c>
       <c r="R24" t="n">
-        <v>6852823</v>
+        <v>6852775</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127044451</v>
+        <v>127044491</v>
       </c>
       <c r="B25" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436598</v>
+        <v>436623</v>
       </c>
       <c r="R25" t="n">
-        <v>6852836</v>
+        <v>6852823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127043256</v>
+        <v>127042707</v>
       </c>
       <c r="B26" t="n">
         <v>78779</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437153</v>
+        <v>436693</v>
       </c>
       <c r="R26" t="n">
-        <v>6852858</v>
+        <v>6852823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127043168</v>
+        <v>127044451</v>
       </c>
       <c r="B27" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437048</v>
+        <v>436598</v>
       </c>
       <c r="R27" t="n">
-        <v>6852775</v>
+        <v>6852836</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127044491</v>
+        <v>127043256</v>
       </c>
       <c r="B28" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436623</v>
+        <v>437153</v>
       </c>
       <c r="R28" t="n">
-        <v>6852823</v>
+        <v>6852858</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3604,7 +3604,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127042769</v>
+        <v>127043039</v>
       </c>
       <c r="B32" t="n">
         <v>79609</v>
@@ -3639,13 +3639,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436811</v>
+        <v>436949</v>
       </c>
       <c r="R32" t="n">
-        <v>6852876</v>
+        <v>6852713</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127043039</v>
+        <v>127042769</v>
       </c>
       <c r="B33" t="n">
         <v>79609</v>
@@ -3736,13 +3736,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436949</v>
+        <v>436811</v>
       </c>
       <c r="R33" t="n">
-        <v>6852713</v>
+        <v>6852876</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127042916</v>
+        <v>127045435</v>
       </c>
       <c r="B4" t="n">
-        <v>79609</v>
+        <v>77998</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436818</v>
+        <v>436671</v>
       </c>
       <c r="R4" t="n">
-        <v>6852702</v>
+        <v>6852588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127045435</v>
+        <v>127042916</v>
       </c>
       <c r="B5" t="n">
-        <v>77998</v>
+        <v>79609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436671</v>
+        <v>436818</v>
       </c>
       <c r="R5" t="n">
-        <v>6852588</v>
+        <v>6852702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127045829</v>
+        <v>127043665</v>
       </c>
       <c r="B7" t="n">
-        <v>79609</v>
+        <v>57767</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436614</v>
+        <v>436739</v>
       </c>
       <c r="R7" t="n">
-        <v>6852662</v>
+        <v>6852982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127042774</v>
+        <v>127045829</v>
       </c>
       <c r="B8" t="n">
-        <v>78779</v>
+        <v>79609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1301,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436811</v>
+        <v>436614</v>
       </c>
       <c r="R8" t="n">
-        <v>6852876</v>
+        <v>6852662</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1354,57 +1363,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127043665</v>
+        <v>127042774</v>
       </c>
       <c r="B9" t="n">
-        <v>57767</v>
+        <v>78779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436739</v>
+        <v>436811</v>
       </c>
       <c r="R9" t="n">
-        <v>6852982</v>
+        <v>6852876</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127042921</v>
+        <v>127045862</v>
       </c>
       <c r="B11" t="n">
-        <v>78779</v>
+        <v>77998</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436818</v>
+        <v>436614</v>
       </c>
       <c r="R11" t="n">
-        <v>6852702</v>
+        <v>6852662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127042878</v>
+        <v>127042921</v>
       </c>
       <c r="B12" t="n">
         <v>78779</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436744</v>
+        <v>436818</v>
       </c>
       <c r="R12" t="n">
-        <v>6852740</v>
+        <v>6852702</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127045862</v>
+        <v>127042878</v>
       </c>
       <c r="B13" t="n">
-        <v>77998</v>
+        <v>78779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436614</v>
+        <v>436744</v>
       </c>
       <c r="R13" t="n">
-        <v>6852662</v>
+        <v>6852740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127042782</v>
+        <v>127042961</v>
       </c>
       <c r="B16" t="n">
-        <v>56855</v>
+        <v>79638</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436839</v>
+        <v>436878</v>
       </c>
       <c r="R16" t="n">
-        <v>6852857</v>
+        <v>6852688</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2113,11 +2113,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2144,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127042961</v>
+        <v>127043500</v>
       </c>
       <c r="B17" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2155,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2179,13 +2174,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436878</v>
+        <v>436900</v>
       </c>
       <c r="R17" t="n">
-        <v>6852688</v>
+        <v>6852768</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2241,32 +2236,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127043500</v>
+        <v>127042782</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2276,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436900</v>
+        <v>436839</v>
       </c>
       <c r="R18" t="n">
-        <v>6852768</v>
+        <v>6852857</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2312,6 +2307,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127043168</v>
+        <v>127042707</v>
       </c>
       <c r="B24" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437048</v>
+        <v>436693</v>
       </c>
       <c r="R24" t="n">
-        <v>6852775</v>
+        <v>6852823</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127044491</v>
+        <v>127044451</v>
       </c>
       <c r="B25" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436623</v>
+        <v>436598</v>
       </c>
       <c r="R25" t="n">
-        <v>6852823</v>
+        <v>6852836</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127042707</v>
+        <v>127043256</v>
       </c>
       <c r="B26" t="n">
         <v>78779</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436693</v>
+        <v>437153</v>
       </c>
       <c r="R26" t="n">
-        <v>6852823</v>
+        <v>6852858</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127044451</v>
+        <v>127043168</v>
       </c>
       <c r="B27" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436598</v>
+        <v>437048</v>
       </c>
       <c r="R27" t="n">
-        <v>6852836</v>
+        <v>6852775</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127043256</v>
+        <v>127044491</v>
       </c>
       <c r="B28" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437153</v>
+        <v>436623</v>
       </c>
       <c r="R28" t="n">
-        <v>6852858</v>
+        <v>6852823</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127043085</v>
+        <v>127043071</v>
       </c>
       <c r="B29" t="n">
-        <v>56855</v>
+        <v>79609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436966</v>
+        <v>436968</v>
       </c>
       <c r="R29" t="n">
-        <v>6852719</v>
+        <v>6852714</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3379,11 +3379,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3410,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127043071</v>
+        <v>127043085</v>
       </c>
       <c r="B30" t="n">
-        <v>79609</v>
+        <v>56855</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3445,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436968</v>
+        <v>436966</v>
       </c>
       <c r="R30" t="n">
-        <v>6852714</v>
+        <v>6852719</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3481,6 +3476,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3895,52 +3895,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127042671</v>
+        <v>127042693</v>
       </c>
       <c r="B35" t="n">
-        <v>56855</v>
+        <v>78779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436712</v>
+        <v>436690</v>
       </c>
       <c r="R35" t="n">
-        <v>6852917</v>
+        <v>6852851</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3996,48 +3992,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127042693</v>
+        <v>127042671</v>
       </c>
       <c r="B36" t="n">
-        <v>78779</v>
+        <v>56855</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436690</v>
+        <v>436712</v>
       </c>
       <c r="R36" t="n">
-        <v>6852851</v>
+        <v>6852917</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127045418</v>
       </c>
       <c r="B2" t="n">
-        <v>78426</v>
+        <v>78417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127043023</v>
       </c>
       <c r="B3" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127045435</v>
       </c>
       <c r="B4" t="n">
-        <v>77998</v>
+        <v>77989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127042916</v>
       </c>
       <c r="B5" t="n">
-        <v>79609</v>
+        <v>79600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127045757</v>
       </c>
       <c r="B6" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127043665</v>
       </c>
       <c r="B7" t="n">
-        <v>57767</v>
+        <v>57761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127045829</v>
+        <v>127042774</v>
       </c>
       <c r="B8" t="n">
-        <v>79609</v>
+        <v>78770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436614</v>
+        <v>436811</v>
       </c>
       <c r="R8" t="n">
-        <v>6852662</v>
+        <v>6852876</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127042774</v>
+        <v>127045829</v>
       </c>
       <c r="B9" t="n">
-        <v>78779</v>
+        <v>79600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436811</v>
+        <v>436614</v>
       </c>
       <c r="R9" t="n">
-        <v>6852876</v>
+        <v>6852662</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>127043219</v>
       </c>
       <c r="B10" t="n">
-        <v>79609</v>
+        <v>79600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127045862</v>
+        <v>127042878</v>
       </c>
       <c r="B11" t="n">
-        <v>77998</v>
+        <v>78770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436614</v>
+        <v>436744</v>
       </c>
       <c r="R11" t="n">
-        <v>6852662</v>
+        <v>6852740</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
         <v>127042921</v>
       </c>
       <c r="B12" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127042878</v>
+        <v>127045862</v>
       </c>
       <c r="B13" t="n">
-        <v>78779</v>
+        <v>77989</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436744</v>
+        <v>436614</v>
       </c>
       <c r="R13" t="n">
-        <v>6852740</v>
+        <v>6852662</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,7 +1851,7 @@
         <v>127044642</v>
       </c>
       <c r="B14" t="n">
-        <v>79609</v>
+        <v>79600</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>127042640</v>
       </c>
       <c r="B15" t="n">
-        <v>77998</v>
+        <v>77989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>127042961</v>
       </c>
       <c r="B16" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>127043500</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>127042782</v>
       </c>
       <c r="B18" t="n">
-        <v>56855</v>
+        <v>56849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>127044529</v>
       </c>
       <c r="B19" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127043155</v>
+        <v>127044713</v>
       </c>
       <c r="B20" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437036</v>
+        <v>436697</v>
       </c>
       <c r="R20" t="n">
-        <v>6852766</v>
+        <v>6852687</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127044760</v>
+        <v>127042718</v>
       </c>
       <c r="B21" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436777</v>
+        <v>436698</v>
       </c>
       <c r="R21" t="n">
-        <v>6852598</v>
+        <v>6852807</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127044713</v>
+        <v>127043155</v>
       </c>
       <c r="B22" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436697</v>
+        <v>437036</v>
       </c>
       <c r="R22" t="n">
-        <v>6852687</v>
+        <v>6852766</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127042718</v>
+        <v>127044760</v>
       </c>
       <c r="B23" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436698</v>
+        <v>436777</v>
       </c>
       <c r="R23" t="n">
-        <v>6852807</v>
+        <v>6852598</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127042707</v>
+        <v>127044491</v>
       </c>
       <c r="B24" t="n">
-        <v>78779</v>
+        <v>78769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436693</v>
+        <v>436623</v>
       </c>
       <c r="R24" t="n">
         <v>6852823</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127044451</v>
+        <v>127043168</v>
       </c>
       <c r="B25" t="n">
-        <v>78779</v>
+        <v>78769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436598</v>
+        <v>437048</v>
       </c>
       <c r="R25" t="n">
-        <v>6852836</v>
+        <v>6852775</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127043256</v>
+        <v>127044451</v>
       </c>
       <c r="B26" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437153</v>
+        <v>436598</v>
       </c>
       <c r="R26" t="n">
-        <v>6852858</v>
+        <v>6852836</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127043168</v>
+        <v>127042707</v>
       </c>
       <c r="B27" t="n">
-        <v>78778</v>
+        <v>78770</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437048</v>
+        <v>436693</v>
       </c>
       <c r="R27" t="n">
-        <v>6852775</v>
+        <v>6852823</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127044491</v>
+        <v>127043256</v>
       </c>
       <c r="B28" t="n">
-        <v>78778</v>
+        <v>78770</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436623</v>
+        <v>437153</v>
       </c>
       <c r="R28" t="n">
-        <v>6852823</v>
+        <v>6852858</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127043071</v>
+        <v>127043085</v>
       </c>
       <c r="B29" t="n">
-        <v>79609</v>
+        <v>56849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436968</v>
+        <v>436966</v>
       </c>
       <c r="R29" t="n">
-        <v>6852714</v>
+        <v>6852719</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3379,6 +3379,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3405,32 +3410,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127043085</v>
+        <v>127043071</v>
       </c>
       <c r="B30" t="n">
-        <v>56855</v>
+        <v>79600</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3445,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436966</v>
+        <v>436968</v>
       </c>
       <c r="R30" t="n">
-        <v>6852719</v>
+        <v>6852714</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3476,11 +3481,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127043130</v>
+        <v>127043039</v>
       </c>
       <c r="B31" t="n">
-        <v>78687</v>
+        <v>79600</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3518,21 +3518,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437025</v>
+        <v>436949</v>
       </c>
       <c r="R31" t="n">
-        <v>6852728</v>
+        <v>6852713</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127043039</v>
+        <v>127042769</v>
       </c>
       <c r="B32" t="n">
-        <v>79609</v>
+        <v>79600</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,13 +3639,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436949</v>
+        <v>436811</v>
       </c>
       <c r="R32" t="n">
-        <v>6852713</v>
+        <v>6852876</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127042769</v>
+        <v>127043130</v>
       </c>
       <c r="B33" t="n">
-        <v>79609</v>
+        <v>78678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3712,21 +3712,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3736,13 +3736,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436811</v>
+        <v>437025</v>
       </c>
       <c r="R33" t="n">
-        <v>6852876</v>
+        <v>6852728</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>127045928</v>
       </c>
       <c r="B34" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3895,48 +3895,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127042693</v>
+        <v>127042671</v>
       </c>
       <c r="B35" t="n">
-        <v>78779</v>
+        <v>56849</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436690</v>
+        <v>436712</v>
       </c>
       <c r="R35" t="n">
-        <v>6852851</v>
+        <v>6852917</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3992,52 +3996,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127042671</v>
+        <v>127042693</v>
       </c>
       <c r="B36" t="n">
-        <v>56855</v>
+        <v>78770</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436712</v>
+        <v>436690</v>
       </c>
       <c r="R36" t="n">
-        <v>6852917</v>
+        <v>6852851</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127045418</v>
       </c>
       <c r="B2" t="n">
-        <v>78417</v>
+        <v>78426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127043023</v>
       </c>
       <c r="B3" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127045435</v>
       </c>
       <c r="B4" t="n">
-        <v>77989</v>
+        <v>77998</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127042916</v>
       </c>
       <c r="B5" t="n">
-        <v>79600</v>
+        <v>79609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127045757</v>
       </c>
       <c r="B6" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127043665</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>57767</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127042774</v>
+        <v>127045829</v>
       </c>
       <c r="B8" t="n">
-        <v>78770</v>
+        <v>79609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436811</v>
+        <v>436614</v>
       </c>
       <c r="R8" t="n">
-        <v>6852876</v>
+        <v>6852662</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127045829</v>
+        <v>127042774</v>
       </c>
       <c r="B9" t="n">
-        <v>79600</v>
+        <v>78779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436614</v>
+        <v>436811</v>
       </c>
       <c r="R9" t="n">
-        <v>6852662</v>
+        <v>6852876</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>127043219</v>
       </c>
       <c r="B10" t="n">
-        <v>79600</v>
+        <v>79609</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127042878</v>
+        <v>127045862</v>
       </c>
       <c r="B11" t="n">
-        <v>78770</v>
+        <v>77998</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436744</v>
+        <v>436614</v>
       </c>
       <c r="R11" t="n">
-        <v>6852740</v>
+        <v>6852662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,7 +1657,7 @@
         <v>127042921</v>
       </c>
       <c r="B12" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127045862</v>
+        <v>127042878</v>
       </c>
       <c r="B13" t="n">
-        <v>77989</v>
+        <v>78779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436614</v>
+        <v>436744</v>
       </c>
       <c r="R13" t="n">
-        <v>6852662</v>
+        <v>6852740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,7 +1851,7 @@
         <v>127044642</v>
       </c>
       <c r="B14" t="n">
-        <v>79600</v>
+        <v>79609</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>127042640</v>
       </c>
       <c r="B15" t="n">
-        <v>77989</v>
+        <v>77998</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>127042961</v>
       </c>
       <c r="B16" t="n">
-        <v>79629</v>
+        <v>79638</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>127043500</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>127042782</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>56855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>127044529</v>
       </c>
       <c r="B19" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127044713</v>
+        <v>127043155</v>
       </c>
       <c r="B20" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436697</v>
+        <v>437036</v>
       </c>
       <c r="R20" t="n">
-        <v>6852687</v>
+        <v>6852766</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127042718</v>
+        <v>127044760</v>
       </c>
       <c r="B21" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436698</v>
+        <v>436777</v>
       </c>
       <c r="R21" t="n">
-        <v>6852807</v>
+        <v>6852598</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127043155</v>
+        <v>127044713</v>
       </c>
       <c r="B22" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437036</v>
+        <v>436697</v>
       </c>
       <c r="R22" t="n">
-        <v>6852766</v>
+        <v>6852687</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127044760</v>
+        <v>127042718</v>
       </c>
       <c r="B23" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436777</v>
+        <v>436698</v>
       </c>
       <c r="R23" t="n">
-        <v>6852598</v>
+        <v>6852807</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127044491</v>
+        <v>127042707</v>
       </c>
       <c r="B24" t="n">
-        <v>78769</v>
+        <v>78779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436623</v>
+        <v>436693</v>
       </c>
       <c r="R24" t="n">
         <v>6852823</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127043168</v>
+        <v>127044451</v>
       </c>
       <c r="B25" t="n">
-        <v>78769</v>
+        <v>78779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437048</v>
+        <v>436598</v>
       </c>
       <c r="R25" t="n">
-        <v>6852775</v>
+        <v>6852836</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127044451</v>
+        <v>127043256</v>
       </c>
       <c r="B26" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436598</v>
+        <v>437153</v>
       </c>
       <c r="R26" t="n">
-        <v>6852836</v>
+        <v>6852858</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127042707</v>
+        <v>127043168</v>
       </c>
       <c r="B27" t="n">
-        <v>78770</v>
+        <v>78778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,13 +3149,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436693</v>
+        <v>437048</v>
       </c>
       <c r="R27" t="n">
-        <v>6852823</v>
+        <v>6852775</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127043256</v>
+        <v>127044491</v>
       </c>
       <c r="B28" t="n">
-        <v>78770</v>
+        <v>78778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437153</v>
+        <v>436623</v>
       </c>
       <c r="R28" t="n">
-        <v>6852858</v>
+        <v>6852823</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127043085</v>
+        <v>127043071</v>
       </c>
       <c r="B29" t="n">
-        <v>56849</v>
+        <v>79609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436966</v>
+        <v>436968</v>
       </c>
       <c r="R29" t="n">
-        <v>6852719</v>
+        <v>6852714</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3379,11 +3379,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3410,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127043071</v>
+        <v>127043085</v>
       </c>
       <c r="B30" t="n">
-        <v>79600</v>
+        <v>56855</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3445,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436968</v>
+        <v>436966</v>
       </c>
       <c r="R30" t="n">
-        <v>6852714</v>
+        <v>6852719</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3481,6 +3476,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127043039</v>
+        <v>127043130</v>
       </c>
       <c r="B31" t="n">
-        <v>79600</v>
+        <v>78687</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3518,21 +3518,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436949</v>
+        <v>437025</v>
       </c>
       <c r="R31" t="n">
-        <v>6852713</v>
+        <v>6852728</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127042769</v>
+        <v>127043039</v>
       </c>
       <c r="B32" t="n">
-        <v>79600</v>
+        <v>79609</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,13 +3639,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436811</v>
+        <v>436949</v>
       </c>
       <c r="R32" t="n">
-        <v>6852876</v>
+        <v>6852713</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127043130</v>
+        <v>127042769</v>
       </c>
       <c r="B33" t="n">
-        <v>78678</v>
+        <v>79609</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3712,21 +3712,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3736,13 +3736,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>437025</v>
+        <v>436811</v>
       </c>
       <c r="R33" t="n">
-        <v>6852728</v>
+        <v>6852876</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>127045928</v>
       </c>
       <c r="B34" t="n">
-        <v>78769</v>
+        <v>78778</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3895,52 +3895,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127042671</v>
+        <v>127042693</v>
       </c>
       <c r="B35" t="n">
-        <v>56849</v>
+        <v>78779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436712</v>
+        <v>436690</v>
       </c>
       <c r="R35" t="n">
-        <v>6852917</v>
+        <v>6852851</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3996,48 +3992,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127042693</v>
+        <v>127042671</v>
       </c>
       <c r="B36" t="n">
-        <v>78770</v>
+        <v>56855</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436690</v>
+        <v>436712</v>
       </c>
       <c r="R36" t="n">
-        <v>6852851</v>
+        <v>6852917</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127045418</v>
+        <v>127043130</v>
       </c>
       <c r="B2" t="n">
-        <v>78426</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436671</v>
+        <v>437025</v>
       </c>
       <c r="R2" t="n">
-        <v>6852588</v>
+        <v>6852728</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127043023</v>
+        <v>127043500</v>
       </c>
       <c r="B3" t="n">
-        <v>78779</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436949</v>
+        <v>436900</v>
       </c>
       <c r="R3" t="n">
-        <v>6852713</v>
+        <v>6852768</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127045435</v>
+        <v>127045418</v>
       </c>
       <c r="B4" t="n">
-        <v>77998</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127042916</v>
+        <v>127043168</v>
       </c>
       <c r="B5" t="n">
-        <v>79609</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436818</v>
+        <v>437048</v>
       </c>
       <c r="R5" t="n">
-        <v>6852702</v>
+        <v>6852775</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127045757</v>
+        <v>127044491</v>
       </c>
       <c r="B6" t="n">
-        <v>78779</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436652</v>
+        <v>436623</v>
       </c>
       <c r="R6" t="n">
-        <v>6852648</v>
+        <v>6852823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,57 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127043665</v>
+        <v>127045928</v>
       </c>
       <c r="B7" t="n">
-        <v>57767</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436739</v>
+        <v>436580</v>
       </c>
       <c r="R7" t="n">
-        <v>6852982</v>
+        <v>6852655</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1266,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127045829</v>
+        <v>127042961</v>
       </c>
       <c r="B8" t="n">
-        <v>79609</v>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436614</v>
+        <v>436878</v>
       </c>
       <c r="R8" t="n">
-        <v>6852662</v>
+        <v>6852688</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127042774</v>
+        <v>127042640</v>
       </c>
       <c r="B9" t="n">
-        <v>78779</v>
+        <v>78334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436811</v>
+        <v>436612</v>
       </c>
       <c r="R9" t="n">
-        <v>6852876</v>
+        <v>6852981</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1460,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127043219</v>
+        <v>127045435</v>
       </c>
       <c r="B10" t="n">
-        <v>79609</v>
+        <v>78334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437153</v>
+        <v>436671</v>
       </c>
       <c r="R10" t="n">
-        <v>6852858</v>
+        <v>6852588</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,7 +1551,7 @@
         <v>127045862</v>
       </c>
       <c r="B11" t="n">
-        <v>77998</v>
+        <v>78334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,48 +1645,52 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127042921</v>
+        <v>127042671</v>
       </c>
       <c r="B12" t="n">
-        <v>78779</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436818</v>
+        <v>436712</v>
       </c>
       <c r="R12" t="n">
-        <v>6852702</v>
+        <v>6852917</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1751,32 +1746,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127042878</v>
+        <v>127042782</v>
       </c>
       <c r="B13" t="n">
-        <v>78779</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436744</v>
+        <v>436839</v>
       </c>
       <c r="R13" t="n">
-        <v>6852740</v>
+        <v>6852857</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1822,6 +1817,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127044642</v>
+        <v>127043085</v>
       </c>
       <c r="B14" t="n">
-        <v>79609</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436684</v>
+        <v>436966</v>
       </c>
       <c r="R14" t="n">
-        <v>6852712</v>
+        <v>6852719</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1919,6 +1919,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1945,10 +1950,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127042640</v>
+        <v>127043665</v>
       </c>
       <c r="B15" t="n">
-        <v>77998</v>
+        <v>58057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,34 +1961,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6487</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436612</v>
+        <v>436739</v>
       </c>
       <c r="R15" t="n">
-        <v>6852981</v>
+        <v>6852982</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,10 +2056,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127042961</v>
+        <v>127042693</v>
       </c>
       <c r="B16" t="n">
-        <v>79638</v>
+        <v>79085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2067,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2091,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436878</v>
+        <v>436690</v>
       </c>
       <c r="R16" t="n">
-        <v>6852688</v>
+        <v>6852851</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2139,10 +2153,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127043500</v>
+        <v>127042707</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2164,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2188,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436900</v>
+        <v>436693</v>
       </c>
       <c r="R17" t="n">
-        <v>6852768</v>
+        <v>6852823</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,32 +2250,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127042782</v>
+        <v>127042718</v>
       </c>
       <c r="B18" t="n">
-        <v>56855</v>
+        <v>79085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,13 +2285,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436839</v>
+        <v>436698</v>
       </c>
       <c r="R18" t="n">
-        <v>6852857</v>
+        <v>6852807</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2307,11 +2321,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2338,10 +2347,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127044529</v>
+        <v>127042774</v>
       </c>
       <c r="B19" t="n">
-        <v>78779</v>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2373,13 +2382,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436642</v>
+        <v>436811</v>
       </c>
       <c r="R19" t="n">
-        <v>6852804</v>
+        <v>6852876</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2435,10 +2444,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127043155</v>
+        <v>127042878</v>
       </c>
       <c r="B20" t="n">
-        <v>78779</v>
+        <v>79085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,10 +2479,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437036</v>
+        <v>436744</v>
       </c>
       <c r="R20" t="n">
-        <v>6852766</v>
+        <v>6852740</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,10 +2541,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127044760</v>
+        <v>127042921</v>
       </c>
       <c r="B21" t="n">
-        <v>78779</v>
+        <v>79085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,10 +2576,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436777</v>
+        <v>436818</v>
       </c>
       <c r="R21" t="n">
-        <v>6852598</v>
+        <v>6852702</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2629,10 +2638,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127044713</v>
+        <v>127043023</v>
       </c>
       <c r="B22" t="n">
-        <v>78779</v>
+        <v>79085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,10 +2673,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436697</v>
+        <v>436949</v>
       </c>
       <c r="R22" t="n">
-        <v>6852687</v>
+        <v>6852713</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,10 +2735,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127042718</v>
+        <v>127043155</v>
       </c>
       <c r="B23" t="n">
-        <v>78779</v>
+        <v>79085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2761,13 +2770,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436698</v>
+        <v>437036</v>
       </c>
       <c r="R23" t="n">
-        <v>6852807</v>
+        <v>6852766</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2823,10 +2832,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127042707</v>
+        <v>127043256</v>
       </c>
       <c r="B24" t="n">
-        <v>78779</v>
+        <v>79085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2858,10 +2867,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436693</v>
+        <v>437153</v>
       </c>
       <c r="R24" t="n">
-        <v>6852823</v>
+        <v>6852858</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,7 +2932,7 @@
         <v>127044451</v>
       </c>
       <c r="B25" t="n">
-        <v>78779</v>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,10 +3026,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127043256</v>
+        <v>127044529</v>
       </c>
       <c r="B26" t="n">
-        <v>78779</v>
+        <v>79085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,10 +3061,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437153</v>
+        <v>436642</v>
       </c>
       <c r="R26" t="n">
-        <v>6852858</v>
+        <v>6852804</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,10 +3123,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127043168</v>
+        <v>127044713</v>
       </c>
       <c r="B27" t="n">
-        <v>78778</v>
+        <v>79085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3134,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,13 +3158,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437048</v>
+        <v>436697</v>
       </c>
       <c r="R27" t="n">
-        <v>6852775</v>
+        <v>6852687</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,10 +3220,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127044491</v>
+        <v>127044760</v>
       </c>
       <c r="B28" t="n">
-        <v>78778</v>
+        <v>79085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3231,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3255,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436623</v>
+        <v>436777</v>
       </c>
       <c r="R28" t="n">
-        <v>6852823</v>
+        <v>6852598</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,10 +3317,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127043071</v>
+        <v>127045757</v>
       </c>
       <c r="B29" t="n">
-        <v>79609</v>
+        <v>79085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3328,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3352,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436968</v>
+        <v>436652</v>
       </c>
       <c r="R29" t="n">
-        <v>6852714</v>
+        <v>6852648</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,32 +3414,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127043085</v>
+        <v>127042769</v>
       </c>
       <c r="B30" t="n">
-        <v>56855</v>
+        <v>79917</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,13 +3449,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436966</v>
+        <v>436811</v>
       </c>
       <c r="R30" t="n">
-        <v>6852719</v>
+        <v>6852876</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3476,11 +3485,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3507,10 +3511,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127043130</v>
+        <v>127042916</v>
       </c>
       <c r="B31" t="n">
-        <v>78687</v>
+        <v>79917</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3518,21 +3522,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3542,10 +3546,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437025</v>
+        <v>436818</v>
       </c>
       <c r="R31" t="n">
-        <v>6852728</v>
+        <v>6852702</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3607,7 +3611,7 @@
         <v>127043039</v>
       </c>
       <c r="B32" t="n">
-        <v>79609</v>
+        <v>79917</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3701,10 +3705,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127042769</v>
+        <v>127043071</v>
       </c>
       <c r="B33" t="n">
-        <v>79609</v>
+        <v>79917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,13 +3740,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436811</v>
+        <v>436968</v>
       </c>
       <c r="R33" t="n">
-        <v>6852876</v>
+        <v>6852714</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3798,10 +3802,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127045928</v>
+        <v>127043219</v>
       </c>
       <c r="B34" t="n">
-        <v>78778</v>
+        <v>79917</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3809,21 +3813,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3833,13 +3837,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436580</v>
+        <v>437153</v>
       </c>
       <c r="R34" t="n">
-        <v>6852655</v>
+        <v>6852858</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3895,10 +3899,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127042693</v>
+        <v>127044642</v>
       </c>
       <c r="B35" t="n">
-        <v>78779</v>
+        <v>79917</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3906,21 +3910,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3930,13 +3934,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436690</v>
+        <v>436684</v>
       </c>
       <c r="R35" t="n">
-        <v>6852851</v>
+        <v>6852712</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3992,52 +3996,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127042671</v>
+        <v>127045829</v>
       </c>
       <c r="B36" t="n">
-        <v>56855</v>
+        <v>79917</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Holmängena, Holmängena, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436712</v>
+        <v>436614</v>
       </c>
       <c r="R36" t="n">
-        <v>6852917</v>
+        <v>6852662</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>

--- a/artfynd/A 31367-2025 artfynd.xlsx
+++ b/artfynd/A 31367-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127043130</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127043500</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127045418</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127043168</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127044491</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127045928</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127042961</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127042640</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127045435</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127045862</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127042671</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127042782</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1947,6 +2012,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127043085</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2053,6 +2123,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127043665</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2150,6 +2225,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127042693</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2247,6 +2327,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127042707</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2344,6 +2429,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127042718</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2441,6 +2531,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127042774</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2538,6 +2633,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127042878</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2635,6 +2735,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127042921</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2732,6 +2837,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127043023</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2829,6 +2939,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127043155</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2926,6 +3041,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127043256</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3023,6 +3143,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127044451</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3120,6 +3245,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127044529</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3217,6 +3347,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127044713</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3314,6 +3449,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127044760</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3411,6 +3551,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127045757</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3508,6 +3653,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127042769</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3605,6 +3755,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127042916</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3702,6 +3857,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127043039</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3799,6 +3959,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127043071</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3896,6 +4061,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127043219</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3993,6 +4163,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127044642</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4090,8 +4265,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127045829</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>